--- a/StructureDefinition-VunsEfr.xlsx
+++ b/StructureDefinition-VunsEfr.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2457" uniqueCount="489">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2434" uniqueCount="484">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.1</t>
+    <t>0.1.2</t>
   </si>
   <si>
     <t>Name</t>
@@ -425,412 +425,400 @@
     <t>Procedure.extension</t>
   </si>
   <si>
+    <t xml:space="preserve">Extension
+</t>
+  </si>
+  <si>
+    <t>Extension</t>
+  </si>
+  <si>
+    <t>An Extension</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value:url}
+</t>
+  </si>
+  <si>
+    <t>open</t>
+  </si>
+  <si>
+    <t>DomainResource.extension</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
+  </si>
+  <si>
+    <t>Procedure.extension:bodySite</t>
+  </si>
+  <si>
+    <t>bodySite</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {procedure-targetBodyStructure}
+</t>
+  </si>
+  <si>
+    <t>The target point for this procedure</t>
+  </si>
+  <si>
+    <t>The target body site used for this procedure.  Multiple locations are allowed.</t>
+  </si>
+  <si>
+    <t>Procedure.extension:bodySite.id</t>
+  </si>
+  <si>
+    <t>Procedure.extension.id</t>
+  </si>
+  <si>
+    <t>Unique id for inter-element referencing</t>
+  </si>
+  <si>
+    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
+  </si>
+  <si>
+    <t>Element.id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ele-1
+</t>
+  </si>
+  <si>
+    <t>n/a</t>
+  </si>
+  <si>
+    <t>Procedure.extension:bodySite.extension</t>
+  </si>
+  <si>
+    <t>Procedure.extension.extension</t>
+  </si>
+  <si>
+    <t>Extensions are always sliced by (at least) url</t>
+  </si>
+  <si>
+    <t>Element.extension</t>
+  </si>
+  <si>
+    <t>Procedure.extension:bodySite.url</t>
+  </si>
+  <si>
+    <t>Procedure.extension.url</t>
+  </si>
+  <si>
+    <t>identifies the meaning of the extension</t>
+  </si>
+  <si>
+    <t>Source of the definition for the extension code - a logical name or a URL.</t>
+  </si>
+  <si>
+    <t>The definition may point directly to a computable or human-readable definition of the extensibility codes, or it may be a logical URI as declared in some other specification. The definition SHALL be a URI for the Structure Definition defining the extension.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/StructureDefinition/procedure-targetBodyStructure</t>
+  </si>
+  <si>
+    <t>Extension.url</t>
+  </si>
+  <si>
+    <t>Procedure.extension:bodySite.value[x]</t>
+  </si>
+  <si>
+    <t>Procedure.extension.value[x]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(http://hl7.eu/fhir/laboratory/StructureDefinition/BodyStructure-eu-lab)
+</t>
+  </si>
+  <si>
+    <t>Value of extension</t>
+  </si>
+  <si>
+    <t>Value of extension - must be one of a constrained set of the data types (see [Extensibility](http://hl7.org/fhir/R5/extensibility.html) for a list).</t>
+  </si>
+  <si>
+    <t>Extension.value[x]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ext-1
+</t>
+  </si>
+  <si>
+    <t>Procedure.modifierExtension</t>
+  </si>
+  <si>
     <t>extensions
 user content</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension
+    <t>Extensions that cannot be ignored</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the resource and that modifies the understanding of the element that contains it and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and manageable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer is allowed to define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
+Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
+  </si>
+  <si>
+    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
+  </si>
+  <si>
+    <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4/extensibility.html#modifierExtension).</t>
+  </si>
+  <si>
+    <t>DomainResource.modifierExtension</t>
+  </si>
+  <si>
+    <t>Procedure.identifier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Identifier
 </t>
   </si>
   <si>
-    <t>Additional content defined by implementations</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the resource. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">value:url}
+    <t>External Identifiers for this procedure</t>
+  </si>
+  <si>
+    <t>Business identifiers assigned to this procedure by the performer or other systems which remain constant as the resource is updated and is propagated from server to server.</t>
+  </si>
+  <si>
+    <t>This is a business identifier, not a resource identifier (see [discussion](http://hl7.org/fhir/R4/resource.html#identifiers)).  It is best practice for the identifier to only appear on a single resource instance, however business practices may occasionally dictate that multiple resource instances with the same identifier can exist - possibly even with different resource types.  For example, multiple Patient and Person resource instances might share the same social insurance number.</t>
+  </si>
+  <si>
+    <t>Allows identification of the procedure as it is known by various participating systems and in a way that remains consistent across servers.</t>
+  </si>
+  <si>
+    <t>Event.identifier</t>
+  </si>
+  <si>
+    <t>.id</t>
+  </si>
+  <si>
+    <t>FiveWs.identifier</t>
+  </si>
+  <si>
+    <t>Some combination of ORC-2 / ORC-3 / OBR-2 / OBR-3 / IPC-1 / IPC-2 / IPC-3 / IPC-4</t>
+  </si>
+  <si>
+    <t>Procedure.instantiatesCanonical</t>
+  </si>
+  <si>
+    <t xml:space="preserve">canonical(PlanDefinition|ActivityDefinition|Measure|OperationDefinition|Questionnaire)
 </t>
   </si>
   <si>
-    <t>Extensions are always sliced by (at least) url</t>
-  </si>
-  <si>
-    <t>open</t>
-  </si>
-  <si>
-    <t>DomainResource.extension</t>
-  </si>
-  <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
-  </si>
-  <si>
-    <t>Procedure.extension:bodySite</t>
-  </si>
-  <si>
-    <t>bodySite</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {procedure-targetBodyStructure}
+    <t>Instantiates FHIR protocol or definition</t>
+  </si>
+  <si>
+    <t>The URL pointing to a FHIR-defined protocol, guideline, order set or other definition that is adhered to in whole or in part by this Procedure.</t>
+  </si>
+  <si>
+    <t>Event.instantiatesCanonical</t>
+  </si>
+  <si>
+    <t>.outboundRelationship[typeCode=DEFN].target</t>
+  </si>
+  <si>
+    <t>Procedure.instantiatesUri</t>
+  </si>
+  <si>
+    <t>Instantiates external protocol or definition</t>
+  </si>
+  <si>
+    <t>The URL pointing to an externally maintained protocol, guideline, order set or other definition that is adhered to in whole or in part by this Procedure.</t>
+  </si>
+  <si>
+    <t>This might be an HTML page, PDF, etc. or could just be a non-resolvable URI identifier.</t>
+  </si>
+  <si>
+    <t>Event.instantiatesUri</t>
+  </si>
+  <si>
+    <t>Procedure.basedOn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">fulfills
 </t>
   </si>
   <si>
-    <t>The target point for this procedure</t>
-  </si>
-  <si>
-    <t>The target body site used for this procedure.  Multiple locations are allowed.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ele-1
+    <t xml:space="preserve">Reference(CarePlan|ServiceRequest)
 </t>
   </si>
   <si>
-    <t>n/a</t>
-  </si>
-  <si>
-    <t>Procedure.extension:bodySite.id</t>
-  </si>
-  <si>
-    <t>Procedure.extension.id</t>
+    <t>A request for this procedure</t>
+  </si>
+  <si>
+    <t>A reference to a resource that contains details of the request for this procedure.</t>
+  </si>
+  <si>
+    <t>Event.basedOn</t>
+  </si>
+  <si>
+    <t>.outboundRelationship[typeCode=FLFS].target[classCode=(various e.g. PROC, OBS, PCPR, ACT,  moodCode=RQO].code</t>
+  </si>
+  <si>
+    <t>Procedure.partOf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">container
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(Procedure|Observation|MedicationAdministration)
+</t>
+  </si>
+  <si>
+    <t>Part of referenced event</t>
+  </si>
+  <si>
+    <t>A larger event of which this particular procedure is a component or step.</t>
+  </si>
+  <si>
+    <t>The MedicationAdministration resource has a partOf reference to Procedure, but this is not a circular reference.   For example, the anesthesia MedicationAdministration is part of the surgical Procedure (MedicationAdministration.partOf = Procedure).  For example, the procedure to insert the IV port for an IV medication administration is part of the medication administration (Procedure.partOf = MedicationAdministration).</t>
+  </si>
+  <si>
+    <t>Event.partOf</t>
+  </si>
+  <si>
+    <t>.inboundRelationship[typeCode=COMP].source[classCode=SBADM or PROC or OBS, moodCode=EVN]</t>
+  </si>
+  <si>
+    <t>Procedure.status</t>
+  </si>
+  <si>
+    <t>preparation | in-progress | not-done | on-hold | stopped | completed | entered-in-error | unknown</t>
+  </si>
+  <si>
+    <t>A code specifying the state of the procedure. Generally, this will be the in-progress or completed state.</t>
+  </si>
+  <si>
+    <t>The "unknown" code is not to be used to convey other statuses.  The "unknown" code should be used when one of the statuses applies, but the authoring system doesn't know the current state of the procedure.
+This element is labeled as a modifier because the status contains codes that mark the resource as not currently valid.</t>
+  </si>
+  <si>
+    <t>completed</t>
+  </si>
+  <si>
+    <t>required</t>
+  </si>
+  <si>
+    <t>A code specifying the state of the procedure.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/event-status|4.0.1</t>
+  </si>
+  <si>
+    <t>Event.status</t>
+  </si>
+  <si>
+    <t>statusCode</t>
+  </si>
+  <si>
+    <t>FiveWs.status</t>
+  </si>
+  <si>
+    <t>Procedure.statusReason</t>
+  </si>
+  <si>
+    <t>Suspended Reason
+Cancelled Reason</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CodeableConcept
+</t>
+  </si>
+  <si>
+    <t>Reason for current status</t>
+  </si>
+  <si>
+    <t>Captures the reason for the current state of the procedure.</t>
+  </si>
+  <si>
+    <t>This is generally only used for "exception" statuses such as "not-done", "suspended" or "aborted". The reason for performing the event at all is captured in reasonCode, not here.</t>
+  </si>
+  <si>
+    <t>example</t>
+  </si>
+  <si>
+    <t>A code that identifies the reason a procedure was not performed.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/procedure-not-performed-reason</t>
+  </si>
+  <si>
+    <t>Event.statusReason</t>
+  </si>
+  <si>
+    <t>.reason.Observation.value</t>
+  </si>
+  <si>
+    <t>Procedure.category</t>
+  </si>
+  <si>
+    <t>Classification of the procedure</t>
+  </si>
+  <si>
+    <t>A code that classifies the procedure for searching, sorting and display purposes (e.g. "Surgical Procedure").</t>
+  </si>
+  <si>
+    <t>A code that classifies a procedure for searching, sorting and display purposes.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/procedure-category</t>
+  </si>
+  <si>
+    <t>.outboundRelationship[typeCode="COMP].target[classCode="LIST", moodCode="EVN"].code</t>
+  </si>
+  <si>
+    <t>FiveWs.class</t>
+  </si>
+  <si>
+    <t>Procedure.code</t>
+  </si>
+  <si>
+    <t xml:space="preserve">type
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CodeableConcept {http://hl7.org/fhir/uv/ips/StructureDefinition/CodeableConcept-uv-ips}
+</t>
+  </si>
+  <si>
+    <t>Identification of the procedure</t>
+  </si>
+  <si>
+    <t>Identification of the procedure or recording of "absence of relevant procedures" or of "procedures unknown".</t>
+  </si>
+  <si>
+    <t>0..1 to account for primarily narrative only resources.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/uv/ips/ValueSet/procedures-uv-ips</t>
+  </si>
+  <si>
+    <t>Event.code</t>
+  </si>
+  <si>
+    <t>.code</t>
+  </si>
+  <si>
+    <t>FiveWs.what[x]</t>
+  </si>
+  <si>
+    <t>OBR-44/OBR-45</t>
+  </si>
+  <si>
+    <t>Procedure.code.id</t>
   </si>
   <si>
     <t xml:space="preserve">string
 </t>
   </si>
   <si>
-    <t>Unique id for inter-element referencing</t>
-  </si>
-  <si>
-    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
-  </si>
-  <si>
-    <t>Element.id</t>
-  </si>
-  <si>
-    <t>Procedure.extension:bodySite.extension</t>
-  </si>
-  <si>
-    <t>Procedure.extension.extension</t>
+    <t>Procedure.code.extension</t>
+  </si>
+  <si>
+    <t>Additional content defined by implementations</t>
   </si>
   <si>
     <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t>Element.extension</t>
-  </si>
-  <si>
-    <t>Procedure.extension:bodySite.url</t>
-  </si>
-  <si>
-    <t>Procedure.extension.url</t>
-  </si>
-  <si>
-    <t>identifies the meaning of the extension</t>
-  </si>
-  <si>
-    <t>Source of the definition for the extension code - a logical name or a URL.</t>
-  </si>
-  <si>
-    <t>The definition may point directly to a computable or human-readable definition of the extensibility codes, or it may be a logical URI as declared in some other specification. The definition SHALL be a URI for the Structure Definition defining the extension.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/StructureDefinition/procedure-targetBodyStructure</t>
-  </si>
-  <si>
-    <t>Extension.url</t>
-  </si>
-  <si>
-    <t>Procedure.extension:bodySite.value[x]</t>
-  </si>
-  <si>
-    <t>Procedure.extension.value[x]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(http://hl7.eu/fhir/laboratory/StructureDefinition/BodyStructure-eu-lab)
-</t>
-  </si>
-  <si>
-    <t>Value of extension</t>
-  </si>
-  <si>
-    <t>Value of extension - must be one of a constrained set of the data types (see [Extensibility](http://hl7.org/fhir/R4/extensibility.html) for a list).</t>
-  </si>
-  <si>
-    <t>Extension.value[x]</t>
-  </si>
-  <si>
-    <t>Procedure.modifierExtension</t>
-  </si>
-  <si>
-    <t>Extensions that cannot be ignored</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the resource and that modifies the understanding of the element that contains it and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and manageable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer is allowed to define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
-Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
-  </si>
-  <si>
-    <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4/extensibility.html#modifierExtension).</t>
-  </si>
-  <si>
-    <t>DomainResource.modifierExtension</t>
-  </si>
-  <si>
-    <t>Procedure.identifier</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Identifier
-</t>
-  </si>
-  <si>
-    <t>External Identifiers for this procedure</t>
-  </si>
-  <si>
-    <t>Business identifiers assigned to this procedure by the performer or other systems which remain constant as the resource is updated and is propagated from server to server.</t>
-  </si>
-  <si>
-    <t>This is a business identifier, not a resource identifier (see [discussion](http://hl7.org/fhir/R4/resource.html#identifiers)).  It is best practice for the identifier to only appear on a single resource instance, however business practices may occasionally dictate that multiple resource instances with the same identifier can exist - possibly even with different resource types.  For example, multiple Patient and Person resource instances might share the same social insurance number.</t>
-  </si>
-  <si>
-    <t>Allows identification of the procedure as it is known by various participating systems and in a way that remains consistent across servers.</t>
-  </si>
-  <si>
-    <t>Event.identifier</t>
-  </si>
-  <si>
-    <t>.id</t>
-  </si>
-  <si>
-    <t>FiveWs.identifier</t>
-  </si>
-  <si>
-    <t>Some combination of ORC-2 / ORC-3 / OBR-2 / OBR-3 / IPC-1 / IPC-2 / IPC-3 / IPC-4</t>
-  </si>
-  <si>
-    <t>Procedure.instantiatesCanonical</t>
-  </si>
-  <si>
-    <t xml:space="preserve">canonical(PlanDefinition|ActivityDefinition|Measure|OperationDefinition|Questionnaire)
-</t>
-  </si>
-  <si>
-    <t>Instantiates FHIR protocol or definition</t>
-  </si>
-  <si>
-    <t>The URL pointing to a FHIR-defined protocol, guideline, order set or other definition that is adhered to in whole or in part by this Procedure.</t>
-  </si>
-  <si>
-    <t>see [Canonical References](http://hl7.org/fhir/R4/references.html#canonical)</t>
-  </si>
-  <si>
-    <t>Event.instantiatesCanonical</t>
-  </si>
-  <si>
-    <t>.outboundRelationship[typeCode=DEFN].target</t>
-  </si>
-  <si>
-    <t>Procedure.instantiatesUri</t>
-  </si>
-  <si>
-    <t>Instantiates external protocol or definition</t>
-  </si>
-  <si>
-    <t>The URL pointing to an externally maintained protocol, guideline, order set or other definition that is adhered to in whole or in part by this Procedure.</t>
-  </si>
-  <si>
-    <t>This might be an HTML page, PDF, etc. or could just be a non-resolvable URI identifier.</t>
-  </si>
-  <si>
-    <t>Event.instantiatesUri</t>
-  </si>
-  <si>
-    <t>Procedure.basedOn</t>
-  </si>
-  <si>
-    <t xml:space="preserve">fulfills
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(CarePlan|ServiceRequest)
-</t>
-  </si>
-  <si>
-    <t>A request for this procedure</t>
-  </si>
-  <si>
-    <t>A reference to a resource that contains details of the request for this procedure.</t>
-  </si>
-  <si>
-    <t>References SHALL be a reference to an actual FHIR resource, and SHALL be resolveable (allowing for access control, temporary unavailability, etc.). Resolution can be either by retrieval from the URL, or, where applicable by resource type, by treating an absolute reference as a canonical URL and looking it up in a local registry/repository.</t>
-  </si>
-  <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ref-1:SHALL have a contained resource if a local reference is provided {reference.startsWith('#').not() or (reference.substring(1).trace('url') in %rootResource.contained.id.trace('ids'))}</t>
-  </si>
-  <si>
-    <t>Event.basedOn</t>
-  </si>
-  <si>
-    <t>.outboundRelationship[typeCode=FLFS].target[classCode=(various e.g. PROC, OBS, PCPR, ACT,  moodCode=RQO].code</t>
-  </si>
-  <si>
-    <t>Procedure.partOf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">container
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(Procedure|Observation|MedicationAdministration)
-</t>
-  </si>
-  <si>
-    <t>Part of referenced event</t>
-  </si>
-  <si>
-    <t>A larger event of which this particular procedure is a component or step.</t>
-  </si>
-  <si>
-    <t>The MedicationAdministration resource has a partOf reference to Procedure, but this is not a circular reference.   For example, the anesthesia MedicationAdministration is part of the surgical Procedure (MedicationAdministration.partOf = Procedure).  For example, the procedure to insert the IV port for an IV medication administration is part of the medication administration (Procedure.partOf = MedicationAdministration).</t>
-  </si>
-  <si>
-    <t>Event.partOf</t>
-  </si>
-  <si>
-    <t>.inboundRelationship[typeCode=COMP].source[classCode=SBADM or PROC or OBS, moodCode=EVN]</t>
-  </si>
-  <si>
-    <t>Procedure.status</t>
-  </si>
-  <si>
-    <t>preparation | in-progress | not-done | on-hold | stopped | completed | entered-in-error | unknown</t>
-  </si>
-  <si>
-    <t>A code specifying the state of the procedure. Generally, this will be the in-progress or completed state.</t>
-  </si>
-  <si>
-    <t>The "unknown" code is not to be used to convey other statuses.  The "unknown" code should be used when one of the statuses applies, but the authoring system doesn't know the current state of the procedure.
-This element is labeled as a modifier because the status contains codes that mark the resource as not currently valid.</t>
-  </si>
-  <si>
-    <t>completed</t>
-  </si>
-  <si>
-    <t>required</t>
-  </si>
-  <si>
-    <t>A code specifying the state of the procedure.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/event-status|4.0.1</t>
-  </si>
-  <si>
-    <t>Event.status</t>
-  </si>
-  <si>
-    <t>statusCode</t>
-  </si>
-  <si>
-    <t>FiveWs.status</t>
-  </si>
-  <si>
-    <t>Procedure.statusReason</t>
-  </si>
-  <si>
-    <t>Suspended Reason
-Cancelled Reason</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CodeableConcept
-</t>
-  </si>
-  <si>
-    <t>Reason for current status</t>
-  </si>
-  <si>
-    <t>Captures the reason for the current state of the procedure.</t>
-  </si>
-  <si>
-    <t>This is generally only used for "exception" statuses such as "not-done", "suspended" or "aborted". The reason for performing the event at all is captured in reasonCode, not here.</t>
-  </si>
-  <si>
-    <t>example</t>
-  </si>
-  <si>
-    <t>A code that identifies the reason a procedure was not performed.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/procedure-not-performed-reason</t>
-  </si>
-  <si>
-    <t>Event.statusReason</t>
-  </si>
-  <si>
-    <t>.reason.Observation.value</t>
-  </si>
-  <si>
-    <t>CE/CNE/CWE</t>
-  </si>
-  <si>
-    <t>Procedure.category</t>
-  </si>
-  <si>
-    <t>Classification of the procedure</t>
-  </si>
-  <si>
-    <t>A code that classifies the procedure for searching, sorting and display purposes (e.g. "Surgical Procedure").</t>
-  </si>
-  <si>
-    <t>Not all terminology uses fit this general pattern. In some cases, models should not use CodeableConcept and use Coding directly and provide their own structure for managing text, codings, translations and the relationship between elements and pre- and post-coordination.</t>
-  </si>
-  <si>
-    <t>A code that classifies a procedure for searching, sorting and display purposes.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/procedure-category</t>
-  </si>
-  <si>
-    <t>.outboundRelationship[typeCode="COMP].target[classCode="LIST", moodCode="EVN"].code</t>
-  </si>
-  <si>
-    <t>FiveWs.class</t>
-  </si>
-  <si>
-    <t>Procedure.code</t>
-  </si>
-  <si>
-    <t xml:space="preserve">type
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CodeableConcept {http://hl7.org/fhir/uv/ips/StructureDefinition/CodeableConcept-uv-ips}
-</t>
-  </si>
-  <si>
-    <t>Concept - reference to a terminology or just  text</t>
-  </si>
-  <si>
-    <t>Identification of the procedure or recording of "absence of relevant procedures" or of "procedures unknown".</t>
-  </si>
-  <si>
-    <t>0..1 to account for primarily narrative only resources.</t>
-  </si>
-  <si>
-    <t>A code to identify a specific procedure .</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/uv/ips/ValueSet/procedures-uv-ips</t>
-  </si>
-  <si>
-    <t>Event.code</t>
-  </si>
-  <si>
-    <t>.code</t>
-  </si>
-  <si>
-    <t>FiveWs.what[x]</t>
-  </si>
-  <si>
-    <t>OBR-44/OBR-45</t>
-  </si>
-  <si>
-    <t>Procedure.code.id</t>
-  </si>
-  <si>
-    <t>Procedure.code.extension</t>
   </si>
   <si>
     <t>Procedure.code.coding</t>
@@ -861,10 +849,10 @@
     <t>CodeableConcept.coding</t>
   </si>
   <si>
-    <t>union(., ./translation)</t>
-  </si>
-  <si>
-    <t>C*E.1-8, C*E.10-22</t>
+    <t>CV</t>
+  </si>
+  <si>
+    <t>CE/CNE/CWE subset one of the sets of component 1-3 or 4-6</t>
   </si>
   <si>
     <t>Procedure.code.text</t>
@@ -994,9 +982,6 @@
     <t>.identifier</t>
   </si>
   <si>
-    <t>CX / EI (occasionally, more often EI maps to a resource id or a URL)</t>
-  </si>
-  <si>
     <t>Procedure.subject.display</t>
   </si>
   <si>
@@ -1315,10 +1300,13 @@
     <t>Procedure.bodySite</t>
   </si>
   <si>
+    <t>Target body sites</t>
+  </si>
+  <si>
     <t>Anatomical location which is the focus of the problem.</t>
   </si>
   <si>
-    <t>Codes describing anatomical locations. May include laterality.</t>
+    <t>If the use case requires attributes from the BodySite resource (e.g. to identify and track separately) then use the standard extension [procedure-targetbodystructure](http://hl7.org/fhir/R4/extension-procedure-targetbodystructure.html).</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/body-site</t>
@@ -1436,9 +1424,6 @@
   </si>
   <si>
     <t>Any other notes and comments about the procedure.</t>
-  </si>
-  <si>
-    <t>For systems that do not have structured annotations, they can simply communicate a single annotation with no author or time.  This element may need to be included in narrative because of the potential for modifying information.  *Annotations SHOULD NOT* be used to communicate "modifying" information that could be computable. (This is a SHOULD because enforcing user behavior is nearly impossible).</t>
   </si>
   <si>
     <t>Event.note</t>
@@ -2829,7 +2814,7 @@
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
-        <v>132</v>
+        <v>19</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
@@ -2848,17 +2833,15 @@
         <v>19</v>
       </c>
       <c r="K9" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="L9" t="s" s="2">
         <v>133</v>
       </c>
-      <c r="L9" t="s" s="2">
+      <c r="M9" t="s" s="2">
         <v>134</v>
       </c>
-      <c r="M9" t="s" s="2">
-        <v>135</v>
-      </c>
-      <c r="N9" t="s" s="2">
-        <v>136</v>
-      </c>
+      <c r="N9" s="2"/>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
         <v>19</v>
@@ -2895,19 +2878,17 @@
         <v>19</v>
       </c>
       <c r="AB9" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="AC9" s="2"/>
+      <c r="AD9" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AE9" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="AF9" t="s" s="2">
         <v>137</v>
-      </c>
-      <c r="AC9" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="AD9" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AE9" t="s" s="2">
-        <v>139</v>
-      </c>
-      <c r="AF9" t="s" s="2">
-        <v>140</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>77</v>
@@ -2919,13 +2900,13 @@
         <v>19</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="AK9" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AL9" t="s" s="2">
-        <v>130</v>
+        <v>19</v>
       </c>
       <c r="AM9" t="s" s="2">
         <v>19</v>
@@ -2936,16 +2917,16 @@
     </row>
     <row r="10" hidden="true">
       <c r="A10" t="s" s="2">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="B10" t="s" s="2">
         <v>131</v>
       </c>
       <c r="C10" t="s" s="2">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="D10" t="s" s="2">
-        <v>132</v>
+        <v>19</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
@@ -2964,17 +2945,15 @@
         <v>19</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>146</v>
-      </c>
-      <c r="N10" t="s" s="2">
-        <v>136</v>
-      </c>
+        <v>143</v>
+      </c>
+      <c r="N10" s="2"/>
       <c r="O10" s="2"/>
       <c r="P10" t="s" s="2">
         <v>19</v>
@@ -3023,7 +3002,7 @@
         <v>19</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>77</v>
@@ -3032,16 +3011,16 @@
         <v>78</v>
       </c>
       <c r="AI10" t="s" s="2">
-        <v>147</v>
+        <v>19</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="AK10" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AL10" t="s" s="2">
-        <v>148</v>
+        <v>19</v>
       </c>
       <c r="AM10" t="s" s="2">
         <v>19</v>
@@ -3052,10 +3031,10 @@
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -3078,13 +3057,13 @@
         <v>19</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>151</v>
+        <v>88</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
@@ -3135,7 +3114,7 @@
         <v>19</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>77</v>
@@ -3144,7 +3123,7 @@
         <v>86</v>
       </c>
       <c r="AI11" t="s" s="2">
-        <v>19</v>
+        <v>149</v>
       </c>
       <c r="AJ11" t="s" s="2">
         <v>19</v>
@@ -3153,7 +3132,7 @@
         <v>19</v>
       </c>
       <c r="AL11" t="s" s="2">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="AM11" t="s" s="2">
         <v>19</v>
@@ -3164,14 +3143,14 @@
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
-        <v>132</v>
+        <v>19</v>
       </c>
       <c r="E12" s="2"/>
       <c r="F12" t="s" s="2">
@@ -3190,17 +3169,15 @@
         <v>19</v>
       </c>
       <c r="K12" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="L12" t="s" s="2">
         <v>133</v>
       </c>
-      <c r="L12" t="s" s="2">
+      <c r="M12" t="s" s="2">
         <v>134</v>
       </c>
-      <c r="M12" t="s" s="2">
-        <v>157</v>
-      </c>
-      <c r="N12" t="s" s="2">
-        <v>136</v>
-      </c>
+      <c r="N12" s="2"/>
       <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
         <v>19</v>
@@ -3237,19 +3214,19 @@
         <v>19</v>
       </c>
       <c r="AB12" t="s" s="2">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="AC12" t="s" s="2">
-        <v>138</v>
+        <v>153</v>
       </c>
       <c r="AD12" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AE12" t="s" s="2">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>77</v>
@@ -3261,13 +3238,13 @@
         <v>19</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="AK12" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AL12" t="s" s="2">
-        <v>148</v>
+        <v>19</v>
       </c>
       <c r="AM12" t="s" s="2">
         <v>19</v>
@@ -3278,10 +3255,10 @@
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -3307,13 +3284,13 @@
         <v>100</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -3321,7 +3298,7 @@
       </c>
       <c r="Q13" s="2"/>
       <c r="R13" t="s" s="2">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="S13" t="s" s="2">
         <v>19</v>
@@ -3363,7 +3340,7 @@
         <v>19</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>86</v>
@@ -3392,10 +3369,10 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3418,13 +3395,13 @@
         <v>19</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
@@ -3475,7 +3452,7 @@
         <v>19</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>77</v>
@@ -3484,7 +3461,7 @@
         <v>86</v>
       </c>
       <c r="AI14" t="s" s="2">
-        <v>19</v>
+        <v>168</v>
       </c>
       <c r="AJ14" t="s" s="2">
         <v>98</v>
@@ -3504,14 +3481,14 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
-        <v>132</v>
+        <v>170</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
@@ -3530,19 +3507,19 @@
         <v>19</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="L15" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="M15" t="s" s="2">
+        <v>172</v>
+      </c>
+      <c r="N15" t="s" s="2">
         <v>173</v>
       </c>
-      <c r="M15" t="s" s="2">
+      <c r="O15" t="s" s="2">
         <v>174</v>
-      </c>
-      <c r="N15" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="O15" t="s" s="2">
-        <v>175</v>
       </c>
       <c r="P15" t="s" s="2">
         <v>19</v>
@@ -3579,19 +3556,19 @@
         <v>19</v>
       </c>
       <c r="AB15" t="s" s="2">
-        <v>137</v>
+        <v>19</v>
       </c>
       <c r="AC15" t="s" s="2">
-        <v>138</v>
+        <v>19</v>
       </c>
       <c r="AD15" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AE15" t="s" s="2">
-        <v>139</v>
+        <v>19</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>77</v>
@@ -3603,7 +3580,7 @@
         <v>19</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="AK15" t="s" s="2">
         <v>19</v>
@@ -3620,10 +3597,10 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -3646,19 +3623,19 @@
         <v>87</v>
       </c>
       <c r="K16" t="s" s="2">
+        <v>177</v>
+      </c>
+      <c r="L16" t="s" s="2">
         <v>178</v>
       </c>
-      <c r="L16" t="s" s="2">
+      <c r="M16" t="s" s="2">
         <v>179</v>
       </c>
-      <c r="M16" t="s" s="2">
+      <c r="N16" t="s" s="2">
         <v>180</v>
       </c>
-      <c r="N16" t="s" s="2">
+      <c r="O16" t="s" s="2">
         <v>181</v>
-      </c>
-      <c r="O16" t="s" s="2">
-        <v>182</v>
       </c>
       <c r="P16" t="s" s="2">
         <v>19</v>
@@ -3707,7 +3684,7 @@
         <v>19</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>77</v>
@@ -3716,30 +3693,30 @@
         <v>78</v>
       </c>
       <c r="AI16" t="s" s="2">
-        <v>147</v>
+        <v>19</v>
       </c>
       <c r="AJ16" t="s" s="2">
         <v>98</v>
       </c>
       <c r="AK16" t="s" s="2">
+        <v>182</v>
+      </c>
+      <c r="AL16" t="s" s="2">
         <v>183</v>
       </c>
-      <c r="AL16" t="s" s="2">
+      <c r="AM16" t="s" s="2">
         <v>184</v>
       </c>
-      <c r="AM16" t="s" s="2">
+      <c r="AN16" t="s" s="2">
         <v>185</v>
-      </c>
-      <c r="AN16" t="s" s="2">
-        <v>186</v>
       </c>
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3762,17 +3739,15 @@
         <v>87</v>
       </c>
       <c r="K17" t="s" s="2">
+        <v>187</v>
+      </c>
+      <c r="L17" t="s" s="2">
         <v>188</v>
       </c>
-      <c r="L17" t="s" s="2">
+      <c r="M17" t="s" s="2">
         <v>189</v>
       </c>
-      <c r="M17" t="s" s="2">
-        <v>190</v>
-      </c>
-      <c r="N17" t="s" s="2">
-        <v>191</v>
-      </c>
+      <c r="N17" s="2"/>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
         <v>19</v>
@@ -3821,7 +3796,7 @@
         <v>19</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>77</v>
@@ -3836,10 +3811,10 @@
         <v>98</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="AM17" t="s" s="2">
         <v>19</v>
@@ -3850,10 +3825,10 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3879,13 +3854,13 @@
         <v>100</v>
       </c>
       <c r="L18" t="s" s="2">
+        <v>193</v>
+      </c>
+      <c r="M18" t="s" s="2">
+        <v>194</v>
+      </c>
+      <c r="N18" t="s" s="2">
         <v>195</v>
-      </c>
-      <c r="M18" t="s" s="2">
-        <v>196</v>
-      </c>
-      <c r="N18" t="s" s="2">
-        <v>197</v>
       </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
@@ -3935,7 +3910,7 @@
         <v>19</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>77</v>
@@ -3950,10 +3925,10 @@
         <v>98</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="AM18" t="s" s="2">
         <v>19</v>
@@ -3964,14 +3939,14 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
@@ -3990,17 +3965,15 @@
         <v>87</v>
       </c>
       <c r="K19" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="L19" t="s" s="2">
+        <v>200</v>
+      </c>
+      <c r="M19" t="s" s="2">
         <v>201</v>
       </c>
-      <c r="L19" t="s" s="2">
-        <v>202</v>
-      </c>
-      <c r="M19" t="s" s="2">
-        <v>203</v>
-      </c>
-      <c r="N19" t="s" s="2">
-        <v>204</v>
-      </c>
+      <c r="N19" s="2"/>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
         <v>19</v>
@@ -4049,7 +4022,7 @@
         <v>19</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>77</v>
@@ -4058,16 +4031,16 @@
         <v>78</v>
       </c>
       <c r="AI19" t="s" s="2">
-        <v>147</v>
+        <v>19</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>205</v>
+        <v>98</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="AM19" t="s" s="2">
         <v>19</v>
@@ -4078,14 +4051,14 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
@@ -4104,16 +4077,16 @@
         <v>87</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
@@ -4163,7 +4136,7 @@
         <v>19</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>77</v>
@@ -4172,16 +4145,16 @@
         <v>78</v>
       </c>
       <c r="AI20" t="s" s="2">
-        <v>147</v>
+        <v>19</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>205</v>
+        <v>98</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="AM20" t="s" s="2">
         <v>19</v>
@@ -4192,10 +4165,10 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4221,13 +4194,13 @@
         <v>106</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
@@ -4238,7 +4211,7 @@
         <v>19</v>
       </c>
       <c r="S21" t="s" s="2">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="T21" t="s" s="2">
         <v>19</v>
@@ -4253,13 +4226,13 @@
         <v>19</v>
       </c>
       <c r="X21" t="s" s="2">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="Y21" t="s" s="2">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="Z21" t="s" s="2">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="AA21" t="s" s="2">
         <v>19</v>
@@ -4277,7 +4250,7 @@
         <v>19</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>86</v>
@@ -4292,13 +4265,13 @@
         <v>98</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="AN21" t="s" s="2">
         <v>19</v>
@@ -4306,14 +4279,14 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
@@ -4332,16 +4305,16 @@
         <v>87</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
@@ -4367,13 +4340,13 @@
         <v>19</v>
       </c>
       <c r="X22" t="s" s="2">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="Y22" t="s" s="2">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="Z22" t="s" s="2">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="AA22" t="s" s="2">
         <v>19</v>
@@ -4391,7 +4364,7 @@
         <v>19</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>77</v>
@@ -4400,30 +4373,30 @@
         <v>86</v>
       </c>
       <c r="AI22" t="s" s="2">
-        <v>147</v>
+        <v>19</v>
       </c>
       <c r="AJ22" t="s" s="2">
         <v>98</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="AM22" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>238</v>
+        <v>19</v>
       </c>
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>239</v>
+        <v>234</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>239</v>
+        <v>234</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4446,17 +4419,15 @@
         <v>87</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>241</v>
-      </c>
-      <c r="N23" t="s" s="2">
-        <v>242</v>
-      </c>
+        <v>236</v>
+      </c>
+      <c r="N23" s="2"/>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
         <v>19</v>
@@ -4481,13 +4452,13 @@
         <v>19</v>
       </c>
       <c r="X23" t="s" s="2">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="Y23" t="s" s="2">
-        <v>243</v>
+        <v>237</v>
       </c>
       <c r="Z23" t="s" s="2">
-        <v>244</v>
+        <v>238</v>
       </c>
       <c r="AA23" t="s" s="2">
         <v>19</v>
@@ -4505,7 +4476,7 @@
         <v>19</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>239</v>
+        <v>234</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>77</v>
@@ -4514,7 +4485,7 @@
         <v>86</v>
       </c>
       <c r="AI23" t="s" s="2">
-        <v>147</v>
+        <v>19</v>
       </c>
       <c r="AJ23" t="s" s="2">
         <v>98</v>
@@ -4523,25 +4494,25 @@
         <v>19</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>245</v>
+        <v>239</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>246</v>
+        <v>240</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>238</v>
+        <v>19</v>
       </c>
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>248</v>
+        <v>242</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
@@ -4560,19 +4531,17 @@
         <v>87</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>250</v>
+        <v>244</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>251</v>
-      </c>
-      <c r="N24" t="s" s="2">
-        <v>242</v>
-      </c>
+        <v>245</v>
+      </c>
+      <c r="N24" s="2"/>
       <c r="O24" t="s" s="2">
-        <v>252</v>
+        <v>246</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>19</v>
@@ -4599,11 +4568,9 @@
       <c r="X24" t="s" s="2">
         <v>111</v>
       </c>
-      <c r="Y24" t="s" s="2">
-        <v>253</v>
-      </c>
+      <c r="Y24" s="2"/>
       <c r="Z24" t="s" s="2">
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>19</v>
@@ -4621,7 +4588,7 @@
         <v>19</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>77</v>
@@ -4630,30 +4597,30 @@
         <v>86</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>147</v>
+        <v>19</v>
       </c>
       <c r="AJ24" t="s" s="2">
         <v>98</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>255</v>
+        <v>248</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>256</v>
+        <v>249</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>257</v>
+        <v>250</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>258</v>
+        <v>251</v>
       </c>
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>259</v>
+        <v>252</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>259</v>
+        <v>252</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4676,13 +4643,13 @@
         <v>19</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>151</v>
+        <v>253</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -4733,7 +4700,7 @@
         <v>19</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>77</v>
@@ -4751,7 +4718,7 @@
         <v>19</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="AM25" t="s" s="2">
         <v>19</v>
@@ -4762,14 +4729,14 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>260</v>
+        <v>254</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>260</v>
+        <v>254</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>132</v>
+        <v>170</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
@@ -4788,16 +4755,16 @@
         <v>19</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>134</v>
+        <v>255</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>157</v>
+        <v>256</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>136</v>
+        <v>173</v>
       </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
@@ -4835,19 +4802,19 @@
         <v>19</v>
       </c>
       <c r="AB26" t="s" s="2">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="AC26" t="s" s="2">
-        <v>138</v>
+        <v>153</v>
       </c>
       <c r="AD26" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AE26" t="s" s="2">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>77</v>
@@ -4859,13 +4826,13 @@
         <v>19</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="AK26" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="AM26" t="s" s="2">
         <v>19</v>
@@ -4876,10 +4843,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4899,22 +4866,22 @@
         <v>19</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>87</v>
+        <v>19</v>
       </c>
       <c r="K27" t="s" s="2">
+        <v>258</v>
+      </c>
+      <c r="L27" t="s" s="2">
+        <v>259</v>
+      </c>
+      <c r="M27" t="s" s="2">
+        <v>260</v>
+      </c>
+      <c r="N27" t="s" s="2">
+        <v>261</v>
+      </c>
+      <c r="O27" t="s" s="2">
         <v>262</v>
-      </c>
-      <c r="L27" t="s" s="2">
-        <v>263</v>
-      </c>
-      <c r="M27" t="s" s="2">
-        <v>264</v>
-      </c>
-      <c r="N27" t="s" s="2">
-        <v>265</v>
-      </c>
-      <c r="O27" t="s" s="2">
-        <v>266</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>19</v>
@@ -4924,7 +4891,7 @@
         <v>19</v>
       </c>
       <c r="S27" t="s" s="2">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="T27" t="s" s="2">
         <v>19</v>
@@ -4963,7 +4930,7 @@
         <v>19</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>77</v>
@@ -4972,7 +4939,7 @@
         <v>78</v>
       </c>
       <c r="AI27" t="s" s="2">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="AJ27" t="s" s="2">
         <v>98</v>
@@ -4981,21 +4948,21 @@
         <v>19</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="AM27" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>270</v>
+        <v>266</v>
       </c>
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5018,19 +4985,19 @@
         <v>87</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>151</v>
+        <v>253</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="O28" t="s" s="2">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>19</v>
@@ -5040,7 +5007,7 @@
         <v>19</v>
       </c>
       <c r="S28" t="s" s="2">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="T28" t="s" s="2">
         <v>19</v>
@@ -5079,7 +5046,7 @@
         <v>19</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>77</v>
@@ -5097,25 +5064,25 @@
         <v>19</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="AM28" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>279</v>
+        <v>275</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
@@ -5134,17 +5101,15 @@
         <v>87</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>284</v>
-      </c>
-      <c r="N29" t="s" s="2">
-        <v>204</v>
-      </c>
+        <v>280</v>
+      </c>
+      <c r="N29" s="2"/>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
         <v>19</v>
@@ -5193,7 +5158,7 @@
         <v>19</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>86</v>
@@ -5202,30 +5167,30 @@
         <v>86</v>
       </c>
       <c r="AI29" t="s" s="2">
-        <v>147</v>
+        <v>19</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>205</v>
+        <v>98</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>288</v>
+        <v>284</v>
       </c>
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5248,13 +5213,13 @@
         <v>19</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>151</v>
+        <v>253</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -5305,7 +5270,7 @@
         <v>19</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>77</v>
@@ -5323,7 +5288,7 @@
         <v>19</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="AM30" t="s" s="2">
         <v>19</v>
@@ -5334,14 +5299,14 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
-        <v>132</v>
+        <v>170</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
@@ -5360,16 +5325,16 @@
         <v>19</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>134</v>
+        <v>255</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>157</v>
+        <v>256</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>136</v>
+        <v>173</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -5407,19 +5372,19 @@
         <v>19</v>
       </c>
       <c r="AB31" t="s" s="2">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="AC31" t="s" s="2">
-        <v>138</v>
+        <v>153</v>
       </c>
       <c r="AD31" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AE31" t="s" s="2">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>77</v>
@@ -5431,13 +5396,13 @@
         <v>19</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="AK31" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="AM31" t="s" s="2">
         <v>19</v>
@@ -5448,10 +5413,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>291</v>
+        <v>287</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>291</v>
+        <v>287</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5474,16 +5439,16 @@
         <v>87</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>151</v>
+        <v>253</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>294</v>
+        <v>290</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -5533,7 +5498,7 @@
         <v>19</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>77</v>
@@ -5542,7 +5507,7 @@
         <v>86</v>
       </c>
       <c r="AI32" t="s" s="2">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="AJ32" t="s" s="2">
         <v>98</v>
@@ -5562,10 +5527,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5591,13 +5556,13 @@
         <v>100</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>299</v>
+        <v>295</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
@@ -5623,13 +5588,13 @@
         <v>19</v>
       </c>
       <c r="X33" t="s" s="2">
-        <v>301</v>
+        <v>297</v>
       </c>
       <c r="Y33" t="s" s="2">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="Z33" t="s" s="2">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="AA33" t="s" s="2">
         <v>19</v>
@@ -5647,7 +5612,7 @@
         <v>19</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>77</v>
@@ -5676,10 +5641,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5702,16 +5667,16 @@
         <v>87</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>306</v>
+        <v>302</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
@@ -5761,7 +5726,7 @@
         <v>19</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>77</v>
@@ -5770,7 +5735,7 @@
         <v>86</v>
       </c>
       <c r="AI34" t="s" s="2">
-        <v>147</v>
+        <v>19</v>
       </c>
       <c r="AJ34" t="s" s="2">
         <v>98</v>
@@ -5779,21 +5744,21 @@
         <v>19</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="AM34" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>311</v>
+        <v>19</v>
       </c>
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>312</v>
+        <v>307</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>312</v>
+        <v>307</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5816,16 +5781,16 @@
         <v>87</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>151</v>
+        <v>253</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>313</v>
+        <v>308</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>314</v>
+        <v>309</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>315</v>
+        <v>310</v>
       </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
@@ -5875,7 +5840,7 @@
         <v>19</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>316</v>
+        <v>311</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>77</v>
@@ -5904,10 +5869,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>317</v>
+        <v>312</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>317</v>
+        <v>312</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5930,16 +5895,16 @@
         <v>87</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>319</v>
+        <v>314</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>320</v>
+        <v>315</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
@@ -5989,7 +5954,7 @@
         <v>19</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>317</v>
+        <v>312</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>77</v>
@@ -5998,30 +5963,30 @@
         <v>86</v>
       </c>
       <c r="AI36" t="s" s="2">
-        <v>147</v>
+        <v>19</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>205</v>
+        <v>98</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>325</v>
+        <v>320</v>
       </c>
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>326</v>
+        <v>321</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>326</v>
+        <v>321</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6044,16 +6009,16 @@
         <v>87</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>327</v>
+        <v>322</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>328</v>
+        <v>323</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>329</v>
+        <v>324</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
@@ -6103,7 +6068,7 @@
         <v>19</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>326</v>
+        <v>321</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>77</v>
@@ -6112,30 +6077,30 @@
         <v>86</v>
       </c>
       <c r="AI37" t="s" s="2">
-        <v>147</v>
+        <v>19</v>
       </c>
       <c r="AJ37" t="s" s="2">
         <v>98</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>331</v>
+        <v>326</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>332</v>
+        <v>327</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>333</v>
+        <v>328</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>334</v>
+        <v>329</v>
       </c>
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6158,13 +6123,13 @@
         <v>19</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>151</v>
+        <v>253</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -6215,7 +6180,7 @@
         <v>19</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>77</v>
@@ -6233,7 +6198,7 @@
         <v>19</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="AM38" t="s" s="2">
         <v>19</v>
@@ -6244,14 +6209,14 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>336</v>
+        <v>331</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>336</v>
+        <v>331</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>132</v>
+        <v>170</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
@@ -6270,16 +6235,16 @@
         <v>19</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>134</v>
+        <v>255</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>157</v>
+        <v>256</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>136</v>
+        <v>173</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
@@ -6317,19 +6282,19 @@
         <v>19</v>
       </c>
       <c r="AB39" t="s" s="2">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="AC39" t="s" s="2">
-        <v>138</v>
+        <v>153</v>
       </c>
       <c r="AD39" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AE39" t="s" s="2">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>77</v>
@@ -6338,16 +6303,16 @@
         <v>78</v>
       </c>
       <c r="AI39" t="s" s="2">
-        <v>147</v>
+        <v>19</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="AK39" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>130</v>
+        <v>150</v>
       </c>
       <c r="AM39" t="s" s="2">
         <v>19</v>
@@ -6358,16 +6323,16 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>337</v>
+        <v>332</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>336</v>
+        <v>331</v>
       </c>
       <c r="C40" t="s" s="2">
-        <v>338</v>
+        <v>333</v>
       </c>
       <c r="D40" t="s" s="2">
-        <v>132</v>
+        <v>19</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
@@ -6386,17 +6351,15 @@
         <v>19</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>339</v>
+        <v>334</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>340</v>
+        <v>335</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>341</v>
-      </c>
-      <c r="N40" t="s" s="2">
-        <v>136</v>
-      </c>
+        <v>336</v>
+      </c>
+      <c r="N40" s="2"/>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
         <v>19</v>
@@ -6445,7 +6408,7 @@
         <v>19</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>77</v>
@@ -6454,16 +6417,16 @@
         <v>78</v>
       </c>
       <c r="AI40" t="s" s="2">
-        <v>147</v>
+        <v>19</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>342</v>
+        <v>337</v>
       </c>
       <c r="AM40" t="s" s="2">
         <v>19</v>
@@ -6474,10 +6437,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>343</v>
+        <v>338</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>343</v>
+        <v>338</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6500,17 +6463,15 @@
         <v>87</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>344</v>
+        <v>339</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>345</v>
+        <v>340</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>346</v>
-      </c>
-      <c r="N41" t="s" s="2">
-        <v>204</v>
-      </c>
+        <v>341</v>
+      </c>
+      <c r="N41" s="2"/>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
         <v>19</v>
@@ -6559,7 +6520,7 @@
         <v>19</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>343</v>
+        <v>338</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>77</v>
@@ -6568,19 +6529,19 @@
         <v>86</v>
       </c>
       <c r="AI41" t="s" s="2">
-        <v>147</v>
+        <v>19</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>205</v>
+        <v>98</v>
       </c>
       <c r="AK41" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>347</v>
+        <v>342</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>348</v>
+        <v>343</v>
       </c>
       <c r="AN41" t="s" s="2">
         <v>19</v>
@@ -6588,10 +6549,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>349</v>
+        <v>344</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>349</v>
+        <v>344</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6614,17 +6575,15 @@
         <v>87</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>344</v>
+        <v>339</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>350</v>
+        <v>345</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>351</v>
-      </c>
-      <c r="N42" t="s" s="2">
-        <v>204</v>
-      </c>
+        <v>346</v>
+      </c>
+      <c r="N42" s="2"/>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
         <v>19</v>
@@ -6673,7 +6632,7 @@
         <v>19</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>349</v>
+        <v>344</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>77</v>
@@ -6682,19 +6641,19 @@
         <v>86</v>
       </c>
       <c r="AI42" t="s" s="2">
-        <v>147</v>
+        <v>19</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>205</v>
+        <v>98</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>352</v>
+        <v>347</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>353</v>
+        <v>348</v>
       </c>
       <c r="AN42" t="s" s="2">
         <v>19</v>
@@ -6702,10 +6661,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6728,13 +6687,13 @@
         <v>87</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>355</v>
+        <v>350</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>357</v>
+        <v>352</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -6785,7 +6744,7 @@
         <v>19</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>77</v>
@@ -6794,16 +6753,16 @@
         <v>78</v>
       </c>
       <c r="AI43" t="s" s="2">
-        <v>147</v>
+        <v>19</v>
       </c>
       <c r="AJ43" t="s" s="2">
         <v>98</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>358</v>
+        <v>353</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>359</v>
+        <v>354</v>
       </c>
       <c r="AM43" t="s" s="2">
         <v>19</v>
@@ -6814,10 +6773,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>360</v>
+        <v>355</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>360</v>
+        <v>355</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6840,13 +6799,13 @@
         <v>19</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>151</v>
+        <v>253</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -6897,7 +6856,7 @@
         <v>19</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>77</v>
@@ -6915,7 +6874,7 @@
         <v>19</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="AM44" t="s" s="2">
         <v>19</v>
@@ -6926,14 +6885,14 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>361</v>
+        <v>356</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>361</v>
+        <v>356</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>132</v>
+        <v>170</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
@@ -6952,16 +6911,16 @@
         <v>19</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>134</v>
+        <v>255</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>157</v>
+        <v>256</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>136</v>
+        <v>173</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
@@ -6999,19 +6958,19 @@
         <v>19</v>
       </c>
       <c r="AB45" t="s" s="2">
-        <v>137</v>
+        <v>19</v>
       </c>
       <c r="AC45" t="s" s="2">
-        <v>138</v>
+        <v>19</v>
       </c>
       <c r="AD45" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AE45" t="s" s="2">
-        <v>139</v>
+        <v>19</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>77</v>
@@ -7023,13 +6982,13 @@
         <v>19</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="AM45" t="s" s="2">
         <v>19</v>
@@ -7040,14 +6999,14 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>362</v>
+        <v>357</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>362</v>
+        <v>357</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>363</v>
+        <v>358</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
@@ -7066,19 +7025,19 @@
         <v>87</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>364</v>
+        <v>359</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>136</v>
+        <v>173</v>
       </c>
       <c r="O46" t="s" s="2">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>19</v>
@@ -7127,7 +7086,7 @@
         <v>19</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>366</v>
+        <v>361</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>77</v>
@@ -7139,7 +7098,7 @@
         <v>19</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>19</v>
@@ -7156,10 +7115,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7182,19 +7141,17 @@
         <v>87</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>369</v>
-      </c>
-      <c r="N47" t="s" s="2">
-        <v>242</v>
-      </c>
+        <v>364</v>
+      </c>
+      <c r="N47" s="2"/>
       <c r="O47" t="s" s="2">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>19</v>
@@ -7219,13 +7176,13 @@
         <v>19</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="Z47" t="s" s="2">
-        <v>372</v>
+        <v>367</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>19</v>
@@ -7243,7 +7200,7 @@
         <v>19</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>77</v>
@@ -7252,30 +7209,30 @@
         <v>86</v>
       </c>
       <c r="AI47" t="s" s="2">
-        <v>147</v>
+        <v>19</v>
       </c>
       <c r="AJ47" t="s" s="2">
         <v>98</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>373</v>
+        <v>368</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>374</v>
+        <v>369</v>
       </c>
       <c r="AM47" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>375</v>
+        <v>370</v>
       </c>
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>376</v>
+        <v>371</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>376</v>
+        <v>371</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7298,19 +7255,17 @@
         <v>87</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>377</v>
+        <v>372</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>378</v>
+        <v>373</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>379</v>
-      </c>
-      <c r="N48" t="s" s="2">
-        <v>204</v>
-      </c>
+        <v>374</v>
+      </c>
+      <c r="N48" s="2"/>
       <c r="O48" t="s" s="2">
-        <v>380</v>
+        <v>375</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>19</v>
@@ -7359,7 +7314,7 @@
         <v>19</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>376</v>
+        <v>371</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>86</v>
@@ -7368,30 +7323,30 @@
         <v>86</v>
       </c>
       <c r="AI48" t="s" s="2">
-        <v>147</v>
+        <v>19</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>205</v>
+        <v>98</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>381</v>
+        <v>376</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>382</v>
+        <v>377</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>383</v>
+        <v>378</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>384</v>
+        <v>379</v>
       </c>
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>385</v>
+        <v>380</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>385</v>
+        <v>380</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7414,19 +7369,17 @@
         <v>19</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>386</v>
+        <v>381</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>387</v>
+        <v>382</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>388</v>
-      </c>
-      <c r="N49" t="s" s="2">
-        <v>204</v>
-      </c>
+        <v>383</v>
+      </c>
+      <c r="N49" s="2"/>
       <c r="O49" t="s" s="2">
-        <v>389</v>
+        <v>384</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>19</v>
@@ -7475,7 +7428,7 @@
         <v>19</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>385</v>
+        <v>380</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>77</v>
@@ -7484,16 +7437,16 @@
         <v>86</v>
       </c>
       <c r="AI49" t="s" s="2">
-        <v>147</v>
+        <v>19</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>205</v>
+        <v>98</v>
       </c>
       <c r="AK49" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>390</v>
+        <v>385</v>
       </c>
       <c r="AM49" t="s" s="2">
         <v>19</v>
@@ -7504,10 +7457,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>391</v>
+        <v>386</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>391</v>
+        <v>386</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7530,19 +7483,17 @@
         <v>87</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>393</v>
+        <v>388</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>394</v>
-      </c>
-      <c r="N50" t="s" s="2">
-        <v>204</v>
-      </c>
+        <v>389</v>
+      </c>
+      <c r="N50" s="2"/>
       <c r="O50" t="s" s="2">
-        <v>395</v>
+        <v>390</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>19</v>
@@ -7591,7 +7542,7 @@
         <v>19</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>391</v>
+        <v>386</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>77</v>
@@ -7600,19 +7551,19 @@
         <v>86</v>
       </c>
       <c r="AI50" t="s" s="2">
-        <v>147</v>
+        <v>19</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>205</v>
+        <v>98</v>
       </c>
       <c r="AK50" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>396</v>
+        <v>391</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>397</v>
+        <v>392</v>
       </c>
       <c r="AN50" t="s" s="2">
         <v>19</v>
@@ -7620,10 +7571,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>398</v>
+        <v>393</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>398</v>
+        <v>393</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7646,16 +7597,16 @@
         <v>87</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>399</v>
+        <v>394</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>401</v>
+        <v>396</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
@@ -7681,13 +7632,13 @@
         <v>19</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>402</v>
+        <v>397</v>
       </c>
       <c r="Z51" t="s" s="2">
-        <v>403</v>
+        <v>398</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>19</v>
@@ -7705,7 +7656,7 @@
         <v>19</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>398</v>
+        <v>393</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>77</v>
@@ -7714,30 +7665,30 @@
         <v>78</v>
       </c>
       <c r="AI51" t="s" s="2">
-        <v>147</v>
+        <v>19</v>
       </c>
       <c r="AJ51" t="s" s="2">
         <v>98</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>404</v>
+        <v>399</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>405</v>
+        <v>400</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>406</v>
+        <v>401</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>238</v>
+        <v>19</v>
       </c>
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>407</v>
+        <v>402</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>407</v>
+        <v>402</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7760,16 +7711,16 @@
         <v>87</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>408</v>
+        <v>403</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>409</v>
+        <v>404</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>410</v>
+        <v>405</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>411</v>
+        <v>406</v>
       </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
@@ -7819,7 +7770,7 @@
         <v>19</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>407</v>
+        <v>402</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>77</v>
@@ -7828,19 +7779,19 @@
         <v>78</v>
       </c>
       <c r="AI52" t="s" s="2">
-        <v>147</v>
+        <v>19</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>205</v>
+        <v>98</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>412</v>
+        <v>407</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>405</v>
+        <v>400</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>406</v>
+        <v>401</v>
       </c>
       <c r="AN52" t="s" s="2">
         <v>19</v>
@@ -7848,10 +7799,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>413</v>
+        <v>408</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>413</v>
+        <v>408</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7874,16 +7825,16 @@
         <v>87</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>250</v>
+        <v>409</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>242</v>
+        <v>411</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -7911,11 +7862,9 @@
       <c r="X53" t="s" s="2">
         <v>111</v>
       </c>
-      <c r="Y53" t="s" s="2">
-        <v>415</v>
-      </c>
+      <c r="Y53" s="2"/>
       <c r="Z53" t="s" s="2">
-        <v>416</v>
+        <v>412</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>19</v>
@@ -7933,7 +7882,7 @@
         <v>19</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>413</v>
+        <v>408</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>77</v>
@@ -7942,7 +7891,7 @@
         <v>78</v>
       </c>
       <c r="AI53" t="s" s="2">
-        <v>147</v>
+        <v>19</v>
       </c>
       <c r="AJ53" t="s" s="2">
         <v>98</v>
@@ -7951,21 +7900,21 @@
         <v>19</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>417</v>
+        <v>413</v>
       </c>
       <c r="AM53" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>418</v>
+        <v>414</v>
       </c>
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>419</v>
+        <v>415</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>419</v>
+        <v>415</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -7988,16 +7937,16 @@
         <v>87</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>420</v>
+        <v>416</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>421</v>
+        <v>417</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>422</v>
+        <v>418</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -8023,13 +7972,13 @@
         <v>19</v>
       </c>
       <c r="X54" t="s" s="2">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="Y54" t="s" s="2">
-        <v>423</v>
+        <v>419</v>
       </c>
       <c r="Z54" t="s" s="2">
-        <v>424</v>
+        <v>420</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>19</v>
@@ -8047,7 +7996,7 @@
         <v>19</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>419</v>
+        <v>415</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>77</v>
@@ -8056,7 +8005,7 @@
         <v>86</v>
       </c>
       <c r="AI54" t="s" s="2">
-        <v>147</v>
+        <v>19</v>
       </c>
       <c r="AJ54" t="s" s="2">
         <v>98</v>
@@ -8065,21 +8014,21 @@
         <v>19</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>425</v>
+        <v>421</v>
       </c>
       <c r="AM54" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>238</v>
+        <v>19</v>
       </c>
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>426</v>
+        <v>422</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>426</v>
+        <v>422</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8102,16 +8051,16 @@
         <v>19</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>427</v>
+        <v>423</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>428</v>
+        <v>424</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>429</v>
+        <v>425</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>430</v>
+        <v>426</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -8161,7 +8110,7 @@
         <v>19</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>426</v>
+        <v>422</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>77</v>
@@ -8170,16 +8119,16 @@
         <v>78</v>
       </c>
       <c r="AI55" t="s" s="2">
-        <v>147</v>
+        <v>19</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>205</v>
+        <v>98</v>
       </c>
       <c r="AK55" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>431</v>
+        <v>427</v>
       </c>
       <c r="AM55" t="s" s="2">
         <v>19</v>
@@ -8190,10 +8139,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>432</v>
+        <v>428</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>432</v>
+        <v>428</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8216,16 +8165,16 @@
         <v>19</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>433</v>
+        <v>429</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>434</v>
+        <v>430</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>435</v>
+        <v>431</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -8251,13 +8200,13 @@
         <v>19</v>
       </c>
       <c r="X56" t="s" s="2">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="Y56" t="s" s="2">
-        <v>436</v>
+        <v>432</v>
       </c>
       <c r="Z56" t="s" s="2">
-        <v>437</v>
+        <v>433</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>19</v>
@@ -8275,7 +8224,7 @@
         <v>19</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>432</v>
+        <v>428</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>77</v>
@@ -8284,7 +8233,7 @@
         <v>78</v>
       </c>
       <c r="AI56" t="s" s="2">
-        <v>147</v>
+        <v>19</v>
       </c>
       <c r="AJ56" t="s" s="2">
         <v>98</v>
@@ -8293,21 +8242,21 @@
         <v>19</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>438</v>
+        <v>434</v>
       </c>
       <c r="AM56" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>238</v>
+        <v>19</v>
       </c>
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>439</v>
+        <v>435</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>439</v>
+        <v>435</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8330,19 +8279,17 @@
         <v>19</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>440</v>
+        <v>436</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>441</v>
+        <v>437</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>442</v>
-      </c>
-      <c r="N57" t="s" s="2">
-        <v>204</v>
-      </c>
+        <v>438</v>
+      </c>
+      <c r="N57" s="2"/>
       <c r="O57" t="s" s="2">
-        <v>443</v>
+        <v>439</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>19</v>
@@ -8391,7 +8338,7 @@
         <v>19</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>439</v>
+        <v>435</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>77</v>
@@ -8400,16 +8347,16 @@
         <v>78</v>
       </c>
       <c r="AI57" t="s" s="2">
-        <v>147</v>
+        <v>19</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>205</v>
+        <v>98</v>
       </c>
       <c r="AK57" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>438</v>
+        <v>434</v>
       </c>
       <c r="AM57" t="s" s="2">
         <v>19</v>
@@ -8420,10 +8367,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>444</v>
+        <v>440</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>444</v>
+        <v>440</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8446,17 +8393,15 @@
         <v>19</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>445</v>
+        <v>441</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>446</v>
-      </c>
-      <c r="N58" t="s" s="2">
-        <v>242</v>
-      </c>
+        <v>442</v>
+      </c>
+      <c r="N58" s="2"/>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
         <v>19</v>
@@ -8481,13 +8426,13 @@
         <v>19</v>
       </c>
       <c r="X58" t="s" s="2">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="Y58" t="s" s="2">
-        <v>447</v>
+        <v>443</v>
       </c>
       <c r="Z58" t="s" s="2">
-        <v>448</v>
+        <v>444</v>
       </c>
       <c r="AA58" t="s" s="2">
         <v>19</v>
@@ -8505,7 +8450,7 @@
         <v>19</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>444</v>
+        <v>440</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>77</v>
@@ -8514,7 +8459,7 @@
         <v>78</v>
       </c>
       <c r="AI58" t="s" s="2">
-        <v>147</v>
+        <v>19</v>
       </c>
       <c r="AJ58" t="s" s="2">
         <v>98</v>
@@ -8523,21 +8468,21 @@
         <v>19</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>449</v>
+        <v>445</v>
       </c>
       <c r="AM58" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>238</v>
+        <v>19</v>
       </c>
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>450</v>
+        <v>446</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>450</v>
+        <v>446</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8560,17 +8505,15 @@
         <v>19</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>451</v>
+        <v>447</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>452</v>
+        <v>448</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>453</v>
-      </c>
-      <c r="N59" t="s" s="2">
-        <v>454</v>
-      </c>
+        <v>449</v>
+      </c>
+      <c r="N59" s="2"/>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
         <v>19</v>
@@ -8619,7 +8562,7 @@
         <v>19</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>450</v>
+        <v>446</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>77</v>
@@ -8628,30 +8571,30 @@
         <v>78</v>
       </c>
       <c r="AI59" t="s" s="2">
-        <v>147</v>
+        <v>19</v>
       </c>
       <c r="AJ59" t="s" s="2">
         <v>98</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>455</v>
+        <v>450</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>456</v>
+        <v>451</v>
       </c>
       <c r="AM59" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>457</v>
+        <v>452</v>
       </c>
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>458</v>
+        <v>453</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>458</v>
+        <v>453</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8674,13 +8617,13 @@
         <v>19</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>355</v>
+        <v>350</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>459</v>
+        <v>454</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>460</v>
+        <v>455</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -8731,7 +8674,7 @@
         <v>19</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>458</v>
+        <v>453</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>77</v>
@@ -8740,7 +8683,7 @@
         <v>78</v>
       </c>
       <c r="AI60" t="s" s="2">
-        <v>147</v>
+        <v>19</v>
       </c>
       <c r="AJ60" t="s" s="2">
         <v>98</v>
@@ -8749,7 +8692,7 @@
         <v>19</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>461</v>
+        <v>456</v>
       </c>
       <c r="AM60" t="s" s="2">
         <v>19</v>
@@ -8760,10 +8703,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>462</v>
+        <v>457</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>462</v>
+        <v>457</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8786,13 +8729,13 @@
         <v>19</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>151</v>
+        <v>253</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -8843,7 +8786,7 @@
         <v>19</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>77</v>
@@ -8861,7 +8804,7 @@
         <v>19</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="AM61" t="s" s="2">
         <v>19</v>
@@ -8872,14 +8815,14 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>463</v>
+        <v>458</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>463</v>
+        <v>458</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
-        <v>132</v>
+        <v>170</v>
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
@@ -8898,16 +8841,16 @@
         <v>19</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>134</v>
+        <v>255</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>157</v>
+        <v>256</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>136</v>
+        <v>173</v>
       </c>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
@@ -8945,19 +8888,19 @@
         <v>19</v>
       </c>
       <c r="AB62" t="s" s="2">
-        <v>137</v>
+        <v>19</v>
       </c>
       <c r="AC62" t="s" s="2">
-        <v>138</v>
+        <v>19</v>
       </c>
       <c r="AD62" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AE62" t="s" s="2">
-        <v>139</v>
+        <v>19</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>77</v>
@@ -8969,13 +8912,13 @@
         <v>19</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="AK62" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="AM62" t="s" s="2">
         <v>19</v>
@@ -8986,14 +8929,14 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>464</v>
+        <v>459</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>464</v>
+        <v>459</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
-        <v>363</v>
+        <v>358</v>
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
@@ -9012,19 +8955,19 @@
         <v>87</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>364</v>
+        <v>359</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>136</v>
+        <v>173</v>
       </c>
       <c r="O63" t="s" s="2">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>19</v>
@@ -9073,7 +9016,7 @@
         <v>19</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>366</v>
+        <v>361</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>77</v>
@@ -9085,7 +9028,7 @@
         <v>19</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="AK63" t="s" s="2">
         <v>19</v>
@@ -9102,10 +9045,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>465</v>
+        <v>460</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>465</v>
+        <v>460</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9128,17 +9071,15 @@
         <v>19</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>466</v>
+        <v>461</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>467</v>
-      </c>
-      <c r="N64" t="s" s="2">
-        <v>242</v>
-      </c>
+        <v>462</v>
+      </c>
+      <c r="N64" s="2"/>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
         <v>19</v>
@@ -9166,10 +9107,10 @@
         <v>111</v>
       </c>
       <c r="Y64" t="s" s="2">
-        <v>468</v>
+        <v>463</v>
       </c>
       <c r="Z64" t="s" s="2">
-        <v>469</v>
+        <v>464</v>
       </c>
       <c r="AA64" t="s" s="2">
         <v>19</v>
@@ -9187,7 +9128,7 @@
         <v>19</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>465</v>
+        <v>460</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>77</v>
@@ -9196,7 +9137,7 @@
         <v>86</v>
       </c>
       <c r="AI64" t="s" s="2">
-        <v>147</v>
+        <v>19</v>
       </c>
       <c r="AJ64" t="s" s="2">
         <v>98</v>
@@ -9205,21 +9146,21 @@
         <v>19</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>470</v>
+        <v>465</v>
       </c>
       <c r="AM64" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>238</v>
+        <v>19</v>
       </c>
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>471</v>
+        <v>466</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>471</v>
+        <v>466</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9242,17 +9183,15 @@
         <v>19</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>472</v>
+        <v>467</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>473</v>
+        <v>468</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>474</v>
-      </c>
-      <c r="N65" t="s" s="2">
-        <v>204</v>
-      </c>
+        <v>469</v>
+      </c>
+      <c r="N65" s="2"/>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
         <v>19</v>
@@ -9301,7 +9240,7 @@
         <v>19</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>471</v>
+        <v>466</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>86</v>
@@ -9310,16 +9249,16 @@
         <v>86</v>
       </c>
       <c r="AI65" t="s" s="2">
-        <v>147</v>
+        <v>19</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>205</v>
+        <v>98</v>
       </c>
       <c r="AK65" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>475</v>
+        <v>470</v>
       </c>
       <c r="AM65" t="s" s="2">
         <v>19</v>
@@ -9330,10 +9269,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>476</v>
+        <v>471</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>476</v>
+        <v>471</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9356,19 +9295,19 @@
         <v>19</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>477</v>
+        <v>472</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>478</v>
+        <v>473</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>479</v>
+        <v>474</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>480</v>
+        <v>475</v>
       </c>
       <c r="O66" t="s" s="2">
-        <v>481</v>
+        <v>476</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>19</v>
@@ -9417,7 +9356,7 @@
         <v>19</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>476</v>
+        <v>471</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>77</v>
@@ -9426,16 +9365,16 @@
         <v>78</v>
       </c>
       <c r="AI66" t="s" s="2">
-        <v>147</v>
+        <v>19</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>205</v>
+        <v>98</v>
       </c>
       <c r="AK66" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>482</v>
+        <v>477</v>
       </c>
       <c r="AM66" t="s" s="2">
         <v>19</v>
@@ -9446,10 +9385,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>483</v>
+        <v>478</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>483</v>
+        <v>478</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9472,16 +9411,16 @@
         <v>19</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>484</v>
+        <v>479</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>485</v>
+        <v>480</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>480</v>
+        <v>475</v>
       </c>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
@@ -9507,13 +9446,13 @@
         <v>19</v>
       </c>
       <c r="X67" t="s" s="2">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="Y67" t="s" s="2">
-        <v>486</v>
+        <v>481</v>
       </c>
       <c r="Z67" t="s" s="2">
-        <v>487</v>
+        <v>482</v>
       </c>
       <c r="AA67" t="s" s="2">
         <v>19</v>
@@ -9531,7 +9470,7 @@
         <v>19</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>483</v>
+        <v>478</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>77</v>
@@ -9540,7 +9479,7 @@
         <v>78</v>
       </c>
       <c r="AI67" t="s" s="2">
-        <v>147</v>
+        <v>19</v>
       </c>
       <c r="AJ67" t="s" s="2">
         <v>98</v>
@@ -9549,13 +9488,13 @@
         <v>19</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>488</v>
+        <v>483</v>
       </c>
       <c r="AM67" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>238</v>
+        <v>19</v>
       </c>
     </row>
   </sheetData>

--- a/StructureDefinition-VunsEfr.xlsx
+++ b/StructureDefinition-VunsEfr.xlsx
@@ -81,7 +81,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Profile pour les épreuves fonctionnelles respiratoires</t>
+    <t>Profile for pulmonary function tests</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/StructureDefinition-VunsEfr.xlsx
+++ b/StructureDefinition-VunsEfr.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.2</t>
+    <t>0.2.0</t>
   </si>
   <si>
     <t>Name</t>

--- a/StructureDefinition-VunsEfr.xlsx
+++ b/StructureDefinition-VunsEfr.xlsx
@@ -90,7 +90,7 @@
     <t>Copyright</t>
   </si>
   <si>
-    <t>RM@H IG (C) 2025-2025 University Hospital of Liege, GSI Department, Belgium. This implementation guide is free software: you can redistribute it and/or modify it under the terms of the GNU General Public License as published by the Free Software Foundation, either version 3 of the License, or (at your option) any later version. This program is distributed in the hope that it will be useful, but WITHOUT ANY WARRANTY; without even the implied warranty of MERCHANTABILITY or FITNESS FOR A PARTICULAR PURPOSE. See the GNU General Public License for more details. You should have received a copy of the GNU General Public License along with this program. If not, see &lt;http://www.gnu.org/licenses/&gt;.</t>
+    <t>VUNS IG (C) 2025-2025 University Hospital of Liege, GSI Department, Belgium. This implementation guide is free software: you can redistribute it and/or modify it under the terms of the GNU General Public License as published by the Free Software Foundation, either version 3 of the License, or (at your option) any later version. This program is distributed in the hope that it will be useful, but WITHOUT ANY WARRANTY; without even the implied warranty of MERCHANTABILITY or FITNESS FOR A PARTICULAR PURPOSE. See the GNU General Public License for more details. You should have received a copy of the GNU General Public License along with this program. If not, see &lt;http://www.gnu.org/licenses/&gt;.</t>
   </si>
   <si>
     <t>FHIR Version</t>
